--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -268,10 +268,10 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 17/08/2026 12:36  •  Edição semanal</t>
+          <t>Gerado em: 24/08/2026 12:41  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$58.74</t>
+          <t>$60.05</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+9.10%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-25.1%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$78.55</t>
+          <t>$80.75</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>+3.18%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$608.68</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+1.78%</t>
+          <t>$563.57</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+10.0%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$222.97</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+1.13%</t>
+          <t>$209.91</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-33.3%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$66.49</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
+          <t>$76.66</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$58.74</t>
+          <t>$60.05</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+9.10%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$78.55</t>
+          <t>$80.75</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>+3.18%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>$608.68</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>+1.78%</t>
+          <t>$563.57</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -1542,9 +1542,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>+1.9%</t>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>$222.97</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>+1.13%</t>
+          <t>$209.91</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>$66.49</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
+          <t>$76.66</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>$585.87</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>+1.94%</t>
+          <t>$551.03</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -1698,9 +1698,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+12.5%</t>
         </is>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -1725,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$53.77</t>
+          <t>$53.87</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+3.28%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$34.42</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+4.81%</t>
+          <t>$35.34</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$225.16</t>
+          <t>$214.72</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>$63,611.32</t>
+          <t>$78,674.32</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+1.90%</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+135.8%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+90.7%</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
@@ -1985,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$1,900.35</t>
+          <t>$2,497.86</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+215.7%</t>
+          <t>+140.2%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,13 +76,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFB800"/>
+      <color rgb="00FF3366"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
+      <b val="1"/>
+      <color rgb="00FFB800"/>
       <sz val="9"/>
     </font>
     <font>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -253,21 +253,24 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -277,7 +280,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 24/08/2026 12:41  •  Edição semanal</t>
+          <t>Gerado em: 31/08/2026 18:43  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$60.05</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+9.10%</t>
+          <t>$54.41</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$80.75</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+6.69%</t>
+          <t>$77.19</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-2.8%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$563.57</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>-1.38%</t>
+          <t>$561.67</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+10.0%</t>
+          <t>+10.4%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$209.91</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>-1.12%</t>
+          <t>$208.95</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.0%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$76.66</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+7.64%</t>
+          <t>$75.08</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-26.7%</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$60.05</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+9.10%</t>
+          <t>$54.41</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1388,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1425,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$80.75</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>+6.69%</t>
+          <t>$77.19</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1440,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1455,260 +1458,260 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>$563.57</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>-1.38%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$561.67</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+10.0%</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>+10.4%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>$209.91</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$208.95</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>-1.30%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-33.0%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>OTAN 5%</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>Defesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>FCX</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Freeport-McMoRan</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$75.08</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>-1.79%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>$55</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-26.7%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>S232 auto</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Northrop Grumman</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>COMPRA</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$539.48</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>-1.12%</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>-33.3%</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>$620</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>+14.9%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>Defesa</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>FCX</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Freeport-McMoRan</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>$76.66</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>+7.64%</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>$55</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>-28.3%</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>S232 auto</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>NOC</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Northrop Grumman</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>COMPRA</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>$551.03</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>-2.28%</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>$620</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>+12.5%</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>OTAN 5%</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$53.87</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-10.9%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$35.34</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>-0.98%</t>
+          <t>$36.78</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+1.66%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>-1.0%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$214.72</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>-0.98%</t>
+          <t>$218.18</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-25.5%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>$78,674.32</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$79,146.00</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+90.7%</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+89.5%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,497.86</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+2.91%</t>
+          <t>$2,488.80</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+140.2%</t>
+          <t>+141.1%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2214,162 +2217,162 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2435,162 +2438,162 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2644,17 +2647,17 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 31/08/2026 18:43  •  Edição semanal</t>
+          <t>Gerado em: 07/09/2026 17:11  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$54.41</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>-3.06%</t>
+          <t>$54.55</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$77.19</t>
+          <t>$75.68</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$561.67</t>
+          <t>$525.32</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+18.0%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$208.95</t>
+          <t>$200.83</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-30.3%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$75.08</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-1.79%</t>
+          <t>$72.75</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-24.4%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$54.41</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-3.06%</t>
+          <t>$54.55</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$77.19</t>
+          <t>$75.68</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$561.67</t>
+          <t>$525.32</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+18.0%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$208.95</t>
+          <t>$200.83</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$75.08</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>-1.79%</t>
+          <t>$72.75</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$539.48</t>
+          <t>$515.02</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-2.50%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$57.53</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$36.78</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+1.66%</t>
+          <t>$37.08</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$218.18</t>
+          <t>$230.40</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$79,146.00</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
+          <t>$79,110.11</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>+89.5%</t>
+          <t>+89.6%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,488.80</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-1.00%</t>
+          <t>$2,488.50</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -268,10 +268,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 07/09/2026 17:11  •  Edição semanal</t>
+          <t>Gerado em: 14/09/2026 17:37  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$54.55</t>
+          <t>$51.42</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+1.80%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-12.5%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$75.68</t>
+          <t>$69.22</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -936,9 +936,9 @@
           <t>$75</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>+8.4%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$525.32</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-1.43%</t>
+          <t>$527.91</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>+17.4%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$200.83</t>
+          <t>$194.91</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-28.2%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$72.75</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+0.26%</t>
+          <t>$69.48</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$54.55</t>
+          <t>$51.42</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+1.80%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$75.68</t>
+          <t>$69.22</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$525.32</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-1.43%</t>
+          <t>$527.91</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1545,9 +1545,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>+18.0%</t>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+17.4%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$200.83</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>-0.64%</t>
+          <t>$194.91</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$72.75</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>+0.26%</t>
+          <t>$69.48</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$515.02</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-2.50%</t>
+          <t>$527.66</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1701,9 +1701,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>+20.4%</t>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$57.53</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
+          <t>$53.43</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$37.08</t>
+          <t>$34.84</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$230.40</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
+          <t>$212.25</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$79,110.11</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
+          <t>$78,784.84</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1961,9 +1961,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+89.6%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+90.4%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,488.50</t>
+          <t>$2,526.26</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+141.1%</t>
+          <t>+137.5%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,11 +76,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
@@ -95,6 +90,11 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,16 +229,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,16 +250,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -271,16 +265,19 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +286,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 14/09/2026 17:37  •  Edição semanal</t>
+          <t>Gerado em: 21/09/2026 17:50  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +868,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$51.42</t>
+          <t>$50.38</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+1.80%</t>
+          <t>+6.60%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-10.7%</t>
         </is>
       </c>
     </row>
@@ -913,12 +910,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$69.22</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-1.90%</t>
+          <t>$70.10</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +935,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>+7.0%</t>
         </is>
       </c>
     </row>
@@ -968,7 +965,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -997,12 +994,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$527.91</t>
+          <t>$533.76</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1010,7 +1007,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1022,7 +1019,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+17.4%</t>
+          <t>+16.2%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1036,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$194.91</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-1.40%</t>
+          <t>$194.39</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1052,7 +1049,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-28.0%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1078,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$69.48</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-2.24%</t>
+          <t>$71.95</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1094,7 +1091,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1106,7 +1103,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
     </row>
@@ -1118,35 +1115,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1191,527 +1188,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>$51.42</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>+1.80%</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>$50.38</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>+6.60%</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>-12.5%</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>-10.7%</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>$69.22</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-1.90%</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>$70.10</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>+1.51%</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>+8.4%</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>+7.0%</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>$527.91</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>+0.71%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>$533.76</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+17.4%</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>+16.2%</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>$194.91</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>-1.40%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>$194.39</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>-28.2%</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>-28.0%</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>$69.48</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>-2.24%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>$71.95</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>-20.8%</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>-23.6%</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>$527.66</t>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>$525.02</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>+1.67%</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>+17.5%</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>+18.1%</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1728,7 +1725,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1737,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$53.43</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>-4.69%</t>
+          <t>$51.60</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1753,9 +1750,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>-10.2%</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1777,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$34.84</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>-2.79%</t>
+          <t>$33.39</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1805,9 +1802,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>+0.5%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1829,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1841,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$212.25</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-2.77%</t>
+          <t>$227.51</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1857,9 +1854,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>-24.6%</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1881,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1909,7 +1906,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1926,52 +1923,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>$78,784.84</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+1.94%</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>$85,806.55</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>+5.52%</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>+90.4%</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>+74.8%</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1988,7 +1985,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +1997,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,526.26</t>
+          <t>$2,737.80</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2012,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+137.5%</t>
+          <t>+119.2%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2037,105 +2034,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2183,196 +2180,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2404,196 +2401,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2623,41 +2620,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2667,56 +2664,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr"/>
+      <c r="C4" s="43" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr"/>
+      <c r="C5" s="43" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr"/>
+      <c r="C6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr"/>
+      <c r="C7" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -76,6 +76,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF3366"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="9"/>
@@ -90,11 +95,6 @@
       <b val="1"/>
       <color rgb="00FFB800"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF3366"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,13 +229,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,34 +253,34 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -286,7 +289,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 21/09/2026 17:50  •  Edição semanal</t>
+          <t>Gerado em: 28/09/2026 19:12  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -868,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$50.38</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+6.60%</t>
+          <t>$46.66</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
@@ -910,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$70.10</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+1.51%</t>
+          <t>$64.60</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -935,7 +938,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+7.0%</t>
+          <t>+16.1%</t>
         </is>
       </c>
     </row>
@@ -965,7 +968,7 @@
           <t>Energia</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -994,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$533.76</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
+          <t>$518.54</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1007,7 +1010,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+19.6%</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$194.39</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
+          <t>$187.23</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1049,7 +1052,7 @@
           <t>Defesa</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-25.2%</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$71.95</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>+0.57%</t>
+          <t>$72.18</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1091,7 +1094,7 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.8%</t>
         </is>
       </c>
     </row>
@@ -1115,35 +1118,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F — Ouro Futuros (95% convicção) → Target: $5,000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F — Prata Futuros (90% convicção) → Target: $58</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP — MP Materials (88% convicção) → Target: $45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX — VanEck Rare Earth ETF (82% convicção) → Target: $75</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TRUMP MINDSET: Tarifas = alavanca, não o fim  •  Deal bilateral assimétrico  •  Doutrina Monroe 2.0  •  Hard assets como hedge estrutural</t>
         </is>
@@ -1188,527 +1191,527 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>WATCHLIST COMPLETA — TRUMP INTEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>SÍMBOLO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>CONVICÇÃO</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>PREÇO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>VAR %</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>UPSIDE</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>CATALISADOR</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>SETOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>GC=F</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Ouro Futuros</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>$5,000</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>SI=F</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Prata Futuros</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>$58</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>MP Materials</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>$50.38</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>+6.60%</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>$46.66</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>-4.44%</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>-10.7%</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>-3.6%</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Summit Xi</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REMX</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>VanEck Rare Earth ETF</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>FORTE COMPRA</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>$70.10</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>+1.51%</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>$64.60</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>-3.09%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>$75</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>+7.0%</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>+16.1%</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NG=F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Gás Natural</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>$6</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>LNG deals</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Energia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>$533.76</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$518.54</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>+16.2%</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>+19.6%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>RTX</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>RTX Corp</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>$194.39</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$187.23</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>-28.0%</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>-25.2%</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>FCX</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Freeport-McMoRan</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>$71.95</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>+0.57%</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>$72.18</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>$55</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>-23.6%</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>-23.8%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>S232 auto</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NOC</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Northrop Grumman</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>$525.02</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>-0.45%</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>$507.09</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>+18.1%</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>+22.3%</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>OTAN 5%</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Defesa</t>
         </is>
@@ -1725,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1737,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$51.60</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+0.94%</t>
+          <t>$51.45</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1750,9 +1753,9 @@
           <t>$48</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-7.0%</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1777,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1789,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$33.39</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>-0.74%</t>
+          <t>$32.57</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1802,9 +1805,9 @@
           <t>$35</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1829,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1841,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$227.51</t>
+          <t>$230.02</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>+2.20%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1854,9 +1857,9 @@
           <t>$160</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>-29.7%</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1881,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>$80</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -1923,52 +1926,52 @@
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>BTC-USD</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>COMPRA</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>$85,806.55</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>+5.52%</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>$83,668.76</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>-1.32%</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>+74.8%</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>+79.3%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
@@ -1985,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1997,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,737.80</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+4.06%</t>
+          <t>$2,684.35</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2012,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+119.2%</t>
+          <t>+123.5%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2034,105 +2037,105 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  GC=F (95%): JP Morgan $5.000/oz. Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SI=F (90%): China elevou a estratégico. Déficit estrutural. Solar +143%.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  MP (88%): Único produtor rare earth EUA em escala. DoD acionista.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  REMX (82%): ETF exposição direta prazo nov/2026. Assimétrico.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NG=F (85%): Deal $33bi Japão. LNG exports. Trump incentiva.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  LMT (83%): OTAN 5% PIB. 4 frentes: Greenland, Venezuela, Irã, Ucrânia.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  RTX (83%): Rearmamento global. Catalisadores independentes de paz.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCX (80%): Maior produtor Cu EUA. Section 232 proteção doméstica.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOC (80%): Defesa espacial + GBSD. OTAN + Indo-Pacífico.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  SLB (75%): Play Venezuela serviços, não preço spot.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  HAL (72%): Venezuela caos pós-Maduro. HAL menos exposto que produtoras.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  NVDA (75%): CapEx IA $3tri. Semicondutores = Section 232.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  CL=F (60%): JP Morgan bearish. Venezuela ramp-up = oversupply potencial.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  BTC-USD (78%): Halving + ETFs spot + Trump pró-cripto. Ciclo Q4/2025–Q1/2026.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  ETH-USD (62%): ETF aprovado. SEC Atkins pró-cripto. Staking yield pendente.</t>
         </is>
@@ -2180,196 +2183,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>TESES GEOPOLÍTICAS — DOUTRINA TRUMP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>TEATRO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>TESE CENTRAL</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>ANÁLISE</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>AÇÃO / PLAY</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Doutrina Monroe 2.0</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Maduro capturado jan/2026. EUA corre Venezuela. 17% reservas mundiais. Condição: cortar China/Rússia/Irã.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>SLB, HAL — SERVIÇOS (não preço spot)</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>China — Raros</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Pausa Nov/2026</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Controles out/2025 suspensos até 10/nov/2026. 7 HREEs ativos. Summit Trump-Xi = catalisador.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>MP, REMX — upside assimétrico</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>SUMMIT 22d</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Reconstrução</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>5 rodadas sem avanço. Zelensky 90% fechado. EUA opera como investidor; Europa paga com empresas americanas.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC, AECOM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>NEGOC.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Europa / OTAN</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Rearmamento</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Alemanha orçamento histórico. Meta 5% PIB. Catalisadores independentes de paz.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>LMT, RTX, NOC</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Tarifas / SCOTUS</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Section 232</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>SCOTUS derrubou IEEPA (fev/2026). Section 122 10%→15%. Section 232 constitucional: aço, alumínio, cobre.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE, HG=F</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>SECTION 232</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Ouro estrutural</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>BCs dedolarizando</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Correlação ouro-dólar quebrou. BCs emergentes 900t/ano. Não é apenas hedge inflacionário — é dedolarização.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV, SI=F</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>ESTRUTURAL</t>
         </is>
@@ -2401,196 +2404,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE GATILHOS 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>IMPACTO</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>ATIVOS RELACIONADOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>31/Mar–2/Abr/2026</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Summit Trump–Xi</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Minerais raros na mesa. MP/REMX ±30% em 24h.</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, SLV</t>
         </is>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Abr/2026</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Section 232 — Automotivo</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Peças automotivas incluídas em tarifas de aço/alumínio.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>FCX, CLF, NUE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Jun/2026</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Tarifas Greenland</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Trump 25% países europeus que bloqueiem acesso.</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>LMT, RTX</t>
         </is>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Nov/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>TRIPLE EVENT</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>CRÍTICO</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Trégua EUA-China + pausa minerais raros + Midterms. 3 em 1.</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>MP, REMX, GLD</t>
         </is>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Revisão USMCA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>MÉDIO</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>México e Canadá vulneráveis a pressões tarifárias.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>FCX, MPC</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Q4/2026</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Ouro $5.000/oz</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Fed dovish + BCs 900t/ano + déficit $2tri+.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>GLD, GC=F, SLV</t>
         </is>
@@ -2620,41 +2623,41 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>HISTÓRICO DE BRIEFINGS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>GERADO EM</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>2026-03-27T10:38</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>📌 **TEMA DO DIA:** Correção pré-summit Trump-Xi com foco em reavaliação de tarifas. Mercado precifica possível acordo sobre minerais raros antes de 31/mar, reduzindo prêmio de escassez em REMX (-5.10%) e MP (-3.80%). Doutrina Trump sinalizando flexibilidade tática antes do encontro para maximizar concessões chinesas.
 🎯 **ATIVO EM DESTAQUE:** LMT (+0.50%). Defesa mantém resiliência com SCOTUS validando Section 232; Venezuela ativa demanda por armamentos e serviços (SLB/HAL como proxy). Posicionamento defensivo contra volatilidade geopolítica estrutural pós-summit.
@@ -2664,56 +2667,56 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr"/>
+      <c r="C4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -268,10 +268,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 28/09/2026 19:12  •  Edição semanal</t>
+          <t>Gerado em: 12/10/2026 20:52  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$46.66</t>
+          <t>$43.36</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-4.44%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -894,9 +894,9 @@
           <t>$45</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$64.60</t>
+          <t>$58.18</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-4.58%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+16.1%</t>
+          <t>+28.9%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$518.54</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
+          <t>$511.88</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+21.1%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$187.23</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
+          <t>$186.66</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$72.18</t>
+          <t>$73.29</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$46.66</t>
+          <t>$43.36</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>-4.44%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$64.60</t>
+          <t>$58.18</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-4.58%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>+16.1%</t>
+          <t>+28.9%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$518.54</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
+          <t>$511.88</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1545,9 +1545,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>+19.6%</t>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>+21.1%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$187.23</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
+          <t>$186.66</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$72.18</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
+          <t>$73.29</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$507.09</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>-0.67%</t>
+          <t>$485.00</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1701,9 +1701,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>+22.3%</t>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>+27.8%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$51.45</t>
+          <t>$48.77</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$32.57</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>-0.58%</t>
+          <t>$32.60</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$230.02</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+2.20%</t>
+          <t>$226.32</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$83,668.76</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>-1.32%</t>
+          <t>$83,147.94</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1961,9 +1961,9 @@
           <t>$150,000</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>+79.3%</t>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>+80.4%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,684.35</t>
+          <t>$2,524.91</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+123.5%</t>
+          <t>+137.6%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 12/10/2026 20:52  •  Edição semanal</t>
+          <t>Gerado em: 19/10/2026 18:17  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$43.36</t>
+          <t>$39.38</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+14.3%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$58.18</t>
+          <t>$53.47</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+28.9%</t>
+          <t>+40.3%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$511.88</t>
+          <t>$553.81</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>+21.1%</t>
+          <t>+12.0%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$186.66</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>+0.37%</t>
+          <t>$193.20</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$73.29</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
+          <t>$69.74</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$43.36</t>
+          <t>$39.38</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1389,9 +1389,9 @@
           <t>$45</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$58.18</t>
+          <t>$53.47</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>+28.9%</t>
+          <t>+40.3%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$511.88</t>
+          <t>$553.81</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>+21.1%</t>
+          <t>+12.0%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$186.66</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>+0.37%</t>
+          <t>$193.20</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$73.29</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>-0.54%</t>
+          <t>$69.74</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$485.00</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>+0.89%</t>
+          <t>$515.17</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>+27.8%</t>
+          <t>+20.3%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$48.77</t>
+          <t>$48.98</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$32.60</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
+          <t>$32.74</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$226.32</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>-1.29%</t>
+          <t>$217.61</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$83,147.94</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>-0.64%</t>
+          <t>$82,018.43</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>+80.4%</t>
+          <t>+82.9%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,524.91</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>-0.56%</t>
+          <t>$2,399.97</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+137.6%</t>
+          <t>+150.0%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">

--- a/data/report_latest.xlsx
+++ b/data/report_latest.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +721,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 19/10/2026 18:17  •  Edição semanal</t>
+          <t>Gerado em: 26/10/2026 18:11  •  Edição semanal</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>$39.38</t>
+          <t>$37.95</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+18.6%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>$53.47</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-1.40%</t>
+          <t>$52.04</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+44.1%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$553.81</t>
+          <t>$630.49</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+4.35%</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1020,9 +1020,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>+12.0%</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$193.20</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>-0.37%</t>
+          <t>$197.24</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$69.74</t>
+          <t>$65.46</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>$39.38</t>
+          <t>$37.95</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+18.6%</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>$53.47</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>-1.40%</t>
+          <t>$52.04</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+44.1%</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>$553.81</t>
+          <t>$630.49</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+4.35%</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -1545,9 +1545,9 @@
           <t>$620</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>+12.0%</t>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>$193.20</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>-0.37%</t>
+          <t>$197.24</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>$69.74</t>
+          <t>$65.46</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>$515.17</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>-0.90%</t>
+          <t>$563.47</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>+20.3%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -1728,7 +1728,7 @@
           <t>SLB Schlumberger</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$48.98</t>
+          <t>$53.01</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1780,7 +1780,7 @@
           <t>Halliburton</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$32.74</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>-2.27%</t>
+          <t>$35.46</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$217.61</t>
+          <t>$216.35</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
           <t>Petróleo WTI</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>$82,018.43</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>+1.11%</t>
+          <t>$80,310.01</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>+82.9%</t>
+          <t>+86.8%</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -1988,7 +1988,7 @@
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>SELETIVO</t>
         </is>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>$2,399.97</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+1.49%</t>
+          <t>$2,326.26</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>+150.0%</t>
+          <t>+157.9%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
